--- a/data/简答题题库.xlsx
+++ b/data/简答题题库.xlsx
@@ -27,7 +27,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="248" uniqueCount="108">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="512" uniqueCount="203">
   <si>
     <t>疾病</t>
   </si>
@@ -351,6 +351,291 @@
   </si>
   <si>
     <t>结合全部情境，讨论肺癌骨转移的综合治疗策略及预后管理。</t>
+  </si>
+  <si>
+    <t>“脑中风的警报”</t>
+  </si>
+  <si>
+    <t>根据情境2，解释缺血性脑卒中的治疗原则及溶栓治疗的适应证。</t>
+  </si>
+  <si>
+    <t>根据情境3，阐述脑梗死恢复期的康复治疗及二级预防措施。</t>
+  </si>
+  <si>
+    <t>结合全部情境，列出脑梗死患者的出院指导及长期管理要点。</t>
+  </si>
+  <si>
+    <t>“半身风云”</t>
+  </si>
+  <si>
+    <t>“惊厥之舞”</t>
+  </si>
+  <si>
+    <t>根据情境1，请总结患者的临床表现，分析癫痫的诊断依据及紧急处理原则。</t>
+  </si>
+  <si>
+    <t>根据情境2，解释脑电图在癫痫诊断中的价值及抗癫痫药物的选择原则。</t>
+  </si>
+  <si>
+    <t>根据情境3，阐述抗癫痫药物的副作用及血药浓度监测的意义。</t>
+  </si>
+  <si>
+    <t>结合全部情境，列出癫痫患者的出院指导及长期管理要点。</t>
+  </si>
+  <si>
+    <t>“隐形的枷锁”</t>
+  </si>
+  <si>
+    <t>根据情境1，请总结患者的临床表现，分析抑郁症的诊断依据及紧急处理原则。</t>
+  </si>
+  <si>
+    <t>根据情境2，解释抗抑郁药物的选择原则及常见副作用。</t>
+  </si>
+  <si>
+    <t>根据情境3，阐述抗抑郁药的治疗疗程及副作用处理。</t>
+  </si>
+  <si>
+    <t>结合全部情境，列出抑郁症患者的出院指导及长期管理要点。</t>
+  </si>
+  <si>
+    <t>“心弦紧绷”</t>
+  </si>
+  <si>
+    <t>根据情境1，请总结患者的临床表现，分析不稳定心绞痛的诊断依据及紧急处理措施。</t>
+  </si>
+  <si>
+    <t>根据情境2，解释冠脉造影的适应证及支架植入术的利弊。</t>
+  </si>
+  <si>
+    <t>根据情境3，阐述冠心病二级预防的药物选择及注意事项。</t>
+  </si>
+  <si>
+    <t>结合全部情境，列出冠心病支架术后患者的出院指导及长期管理要点。</t>
+  </si>
+  <si>
+    <t>“心跳乱了”</t>
+  </si>
+  <si>
+    <t>根据情境1，请总结患者的临床表现，分析房颤的诊断依据及紧急处理措施。</t>
+  </si>
+  <si>
+    <t>根据情境2，解释房颤患者卒中风险评估及抗凝治疗的选择原则。</t>
+  </si>
+  <si>
+    <t>根据情境3，阐述华法林与NOAC的优缺点及监测注意事项。</t>
+  </si>
+  <si>
+    <t>结合全部情境，列出房颤患者的出院指导及长期管理要点。</t>
+  </si>
+  <si>
+    <t>“泵的挣扎”</t>
+  </si>
+  <si>
+    <t>根据情境1，请总结患者的临床表现，分析急性左心衰的诊断依据及紧急处理原则。</t>
+  </si>
+  <si>
+    <t>根据情境2，解释心衰的分期及治疗目标。</t>
+  </si>
+  <si>
+    <t>根据情境3，阐述慢性心衰的药物治疗方案及作用机制。</t>
+  </si>
+  <si>
+    <t>结合全部情境，列出心衰患者的出院指导及长期自我管理要点。</t>
+  </si>
+  <si>
+    <t>“喘息的风箱”</t>
+  </si>
+  <si>
+    <t>根据情境1，请总结患者的临床表现，分析哮喘急性发作的处理原则。</t>
+  </si>
+  <si>
+    <t>根据情境2，解释哮喘的诊断依据及长期控制治疗的药物选择。</t>
+  </si>
+  <si>
+    <t>根据情境3，阐述吸入糖皮质激素的作用机制及注意事项。</t>
+  </si>
+  <si>
+    <t>结合全部情境，列出哮喘患者的出院指导及长期管理要点。</t>
+  </si>
+  <si>
+    <t>“被困的气泡”</t>
+  </si>
+  <si>
+    <t>根据情境1，请总结患者的临床表现，分析气胸的诊断依据及紧急处理措施。</t>
+  </si>
+  <si>
+    <t>根据情境2，解释胸腔闭式引流的适应证及操作注意事项。</t>
+  </si>
+  <si>
+    <t>根据情境3，阐述气胸引流后的观察要点及拔管指征。</t>
+  </si>
+  <si>
+    <t>结合全部情境，列出气胸患者的出院指导及预防复发措施。</t>
+  </si>
+  <si>
+    <t>“沉默的阴影”</t>
+  </si>
+  <si>
+    <t>根据情境1，请总结患者的临床表现，分析肺癌的诊断思路及初步检查。</t>
+  </si>
+  <si>
+    <t>根据情境2，解释肺癌TNM分期的意义及不同期别的治疗原则。</t>
+  </si>
+  <si>
+    <t>根据情境3，阐述ⅢA期肺癌的综合治疗策略（新辅助化疗、手术、放化疗）。</t>
+  </si>
+  <si>
+    <t>结合全部情境，列出肺癌患者的出院指导及长期随访计划。</t>
+  </si>
+  <si>
+    <t>“胃里的火山”</t>
+  </si>
+  <si>
+    <t>根据情境1，请总结患者的临床表现，分析可能的诊断及需要做的检查。</t>
+  </si>
+  <si>
+    <t>根据情境2，解释幽门螺杆菌与消化性溃疡的关系，并说明根除治疗的意义。</t>
+  </si>
+  <si>
+    <t>根据情境3，分析难治性溃疡的可能原因及后续处理原则。</t>
+  </si>
+  <si>
+    <t>结合全部情境，列出消化性溃疡患者出院后的综合建议（饮食、用药、复查、预防复发）。</t>
+  </si>
+  <si>
+    <t>“肝胆风云”</t>
+  </si>
+  <si>
+    <t>根据情境2，解释为什么需要择期手术，并说明腹腔镜胆囊切除术的优缺点。</t>
+  </si>
+  <si>
+    <t>根据情境3，阐述胆总管残余结石的诊断及ERCP取石的适应证。</t>
+  </si>
+  <si>
+    <t>结合全部情境，列出胆囊切除术后患者的饮食指导及复发预防措施。</t>
+  </si>
+  <si>
+    <t>“肠路惊魂”</t>
+  </si>
+  <si>
+    <t>根据情境2，解释结直肠癌的分期依据及治疗方案选择。</t>
+  </si>
+  <si>
+    <t>根据情境3，阐述直肠癌术后辅助化疗和放疗的适应证。</t>
+  </si>
+  <si>
+    <t>结合全部情境，列出结直肠癌患者出院后的随访计划及生活方式建议。</t>
+  </si>
+  <si>
+    <t>“石破天惊”</t>
+  </si>
+  <si>
+    <t>根据情境2，解释体外冲击波碎石的原理、适应证及禁忌证。</t>
+  </si>
+  <si>
+    <t>根据情境3，分析ESWL失败后应如何选择后续治疗，并说明输尿管镜碎石的优缺点。</t>
+  </si>
+  <si>
+    <t>结合全部情境，列出泌尿系结石患者出院后的预防复发措施。</t>
+  </si>
+  <si>
+    <t>“隐秘的河流”</t>
+  </si>
+  <si>
+    <t>根据情境2，解释慢性肾小球肾炎的诊断依据及治疗原则。</t>
+  </si>
+  <si>
+    <t>根据情境3，分析患者肾功能下降的可能原因及后续处理措施。</t>
+  </si>
+  <si>
+    <t>结合全部情境，列出慢性肾脏病患者并发症管理及替代治疗准备的内容。</t>
+  </si>
+  <si>
+    <t>“火海警报”</t>
+  </si>
+  <si>
+    <t>根据情境2，解释急性肾盂肾炎的治疗原则及疗程。</t>
+  </si>
+  <si>
+    <t>根据情境3，分析感染合并结石的处理原则，并说明梗阻解除的重要性。</t>
+  </si>
+  <si>
+    <t>结合全部情境，列出尿路感染患者出院后的预防复发措施。</t>
+  </si>
+  <si>
+    <t>“折翼天使”</t>
+  </si>
+  <si>
+    <t>根据情境1，请总结患儿的临床表现，分析可能的诊断及需要做的检查。</t>
+  </si>
+  <si>
+    <t>根据情境2，解释为什么肱骨髁上骨折需要急诊手术，并说明骨筋膜室综合征的早期识别要点。</t>
+  </si>
+  <si>
+    <t>根据情境3，阐述骨筋膜室综合征的病理生理、诊断及处理原则。</t>
+  </si>
+  <si>
+    <t>结合全部情境，列出肱骨髁上骨折术后患儿的康复指导及远期并发症预防。</t>
+  </si>
+  <si>
+    <t>“行走的齿轮”</t>
+  </si>
+  <si>
+    <t>根据情境2，解释骨关节炎的阶梯治疗原则，并说明各种治疗方法的适应证。</t>
+  </si>
+  <si>
+    <t>根据情境3，阐述人工膝关节置换术的适应证、手术方式及术后早期并发症的预防。</t>
+  </si>
+  <si>
+    <t>结合全部情境，列出骨关节炎患者人工膝关节置换术后的康复计划及长期管理要点。</t>
+  </si>
+  <si>
+    <t>“断桥残雪”</t>
+  </si>
+  <si>
+    <t>根据情境2，解释腰椎间盘突出症的保守治疗原则，并说明神经定位的意义。</t>
+  </si>
+  <si>
+    <t>根据情境3，阐述马尾综合征的临床表现、诊断及紧急手术指征。</t>
+  </si>
+  <si>
+    <t>结合全部情境，列出腰椎间盘突出症患者术后康复指导及预防复发的措施。</t>
+  </si>
+  <si>
+    <t>“糖衣炮弹”</t>
+  </si>
+  <si>
+    <t>根据情境2，解释2型糖尿病的诊断依据及二甲双胍的治疗作用。</t>
+  </si>
+  <si>
+    <t>根据情境3，分析二甲双胍的常见副作用及处理原则，并讨论如何调整降糖方案。</t>
+  </si>
+  <si>
+    <t>结合全部情境，列出2型糖尿病患者出院后的综合管理方案（血糖监测、饮食运动、并发症筛查、随访）。</t>
+  </si>
+  <si>
+    <t>“隐形狂飙”</t>
+  </si>
+  <si>
+    <t>根据情境2，解释Graves病的诊断依据及抗甲状腺药物的治疗原则。</t>
+  </si>
+  <si>
+    <t>根据情境3，阐述抗甲状腺药物导致粒细胞缺乏的识别、处理及替代治疗方案。</t>
+  </si>
+  <si>
+    <t>结合全部情境，列出Graves病患者出院后的长期管理要点（药物、监测、复发预防、妊娠注意事项）。</t>
+  </si>
+  <si>
+    <t>“荷尔蒙迷航”</t>
+  </si>
+  <si>
+    <t>根据情境2，解释多囊卵巢综合征的诊断标准及二甲双胍治疗的作用机制。</t>
+  </si>
+  <si>
+    <t>根据情境3，分析多囊卵巢综合征促排卵治疗的选择、过程及风险。</t>
+  </si>
+  <si>
+    <t>结合全部情境，列出多囊卵巢综合征患者成功妊娠后的孕期管理及远期健康指导。</t>
   </si>
 </sst>
 </file>
@@ -1315,7 +1600,7 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:etc="http://www.wps.cn/officeDocument/2017/etCustomData">
   <sheetPr/>
-  <dimension ref="A1:D81"/>
+  <dimension ref="A1:D169"/>
   <sheetFormatPr defaultColWidth="9" defaultRowHeight="13.5" outlineLevelCol="3"/>
   <cols>
     <col min="1" max="1" width="9.02654867256637" style="1"/>
@@ -2455,6 +2740,1238 @@
         <v>10</v>
       </c>
     </row>
+    <row r="82" spans="1:4">
+      <c r="A82" s="1" t="s">
+        <v>108</v>
+      </c>
+      <c r="B82">
+        <v>1</v>
+      </c>
+      <c r="C82" t="s">
+        <v>47</v>
+      </c>
+      <c r="D82" t="s">
+        <v>6</v>
+      </c>
+    </row>
+    <row r="83" spans="1:4">
+      <c r="A83" s="1" t="s">
+        <v>108</v>
+      </c>
+      <c r="B83">
+        <v>2</v>
+      </c>
+      <c r="C83" t="s">
+        <v>109</v>
+      </c>
+      <c r="D83" t="s">
+        <v>16</v>
+      </c>
+    </row>
+    <row r="84" spans="1:4">
+      <c r="A84" s="1" t="s">
+        <v>108</v>
+      </c>
+      <c r="B84">
+        <v>3</v>
+      </c>
+      <c r="C84" t="s">
+        <v>110</v>
+      </c>
+      <c r="D84" t="s">
+        <v>10</v>
+      </c>
+    </row>
+    <row r="85" spans="1:4">
+      <c r="A85" s="1" t="s">
+        <v>108</v>
+      </c>
+      <c r="B85">
+        <v>4</v>
+      </c>
+      <c r="C85" t="s">
+        <v>111</v>
+      </c>
+      <c r="D85" t="s">
+        <v>10</v>
+      </c>
+    </row>
+    <row r="86" spans="1:4">
+      <c r="A86" s="1" t="s">
+        <v>112</v>
+      </c>
+      <c r="B86">
+        <v>1</v>
+      </c>
+      <c r="C86" t="s">
+        <v>47</v>
+      </c>
+      <c r="D86" t="s">
+        <v>6</v>
+      </c>
+    </row>
+    <row r="87" spans="1:4">
+      <c r="A87" s="1" t="s">
+        <v>112</v>
+      </c>
+      <c r="B87">
+        <v>2</v>
+      </c>
+      <c r="C87" t="s">
+        <v>109</v>
+      </c>
+      <c r="D87" t="s">
+        <v>16</v>
+      </c>
+    </row>
+    <row r="88" spans="1:4">
+      <c r="A88" s="1" t="s">
+        <v>112</v>
+      </c>
+      <c r="B88">
+        <v>3</v>
+      </c>
+      <c r="C88" t="s">
+        <v>110</v>
+      </c>
+      <c r="D88" t="s">
+        <v>10</v>
+      </c>
+    </row>
+    <row r="89" spans="1:4">
+      <c r="A89" s="1" t="s">
+        <v>112</v>
+      </c>
+      <c r="B89">
+        <v>4</v>
+      </c>
+      <c r="C89" t="s">
+        <v>111</v>
+      </c>
+      <c r="D89" t="s">
+        <v>10</v>
+      </c>
+    </row>
+    <row r="90" spans="1:4">
+      <c r="A90" s="1" t="s">
+        <v>113</v>
+      </c>
+      <c r="B90">
+        <v>1</v>
+      </c>
+      <c r="C90" t="s">
+        <v>114</v>
+      </c>
+      <c r="D90" t="s">
+        <v>6</v>
+      </c>
+    </row>
+    <row r="91" spans="1:4">
+      <c r="A91" s="1" t="s">
+        <v>113</v>
+      </c>
+      <c r="B91">
+        <v>2</v>
+      </c>
+      <c r="C91" t="s">
+        <v>115</v>
+      </c>
+      <c r="D91" t="s">
+        <v>16</v>
+      </c>
+    </row>
+    <row r="92" spans="1:4">
+      <c r="A92" s="1" t="s">
+        <v>113</v>
+      </c>
+      <c r="B92">
+        <v>3</v>
+      </c>
+      <c r="C92" t="s">
+        <v>116</v>
+      </c>
+      <c r="D92" t="s">
+        <v>10</v>
+      </c>
+    </row>
+    <row r="93" spans="1:4">
+      <c r="A93" s="1" t="s">
+        <v>113</v>
+      </c>
+      <c r="B93">
+        <v>4</v>
+      </c>
+      <c r="C93" t="s">
+        <v>117</v>
+      </c>
+      <c r="D93" t="s">
+        <v>10</v>
+      </c>
+    </row>
+    <row r="94" spans="1:4">
+      <c r="A94" s="1" t="s">
+        <v>118</v>
+      </c>
+      <c r="B94">
+        <v>1</v>
+      </c>
+      <c r="C94" t="s">
+        <v>119</v>
+      </c>
+      <c r="D94" t="s">
+        <v>6</v>
+      </c>
+    </row>
+    <row r="95" spans="1:4">
+      <c r="A95" s="1" t="s">
+        <v>118</v>
+      </c>
+      <c r="B95">
+        <v>2</v>
+      </c>
+      <c r="C95" t="s">
+        <v>120</v>
+      </c>
+      <c r="D95" t="s">
+        <v>16</v>
+      </c>
+    </row>
+    <row r="96" spans="1:4">
+      <c r="A96" s="1" t="s">
+        <v>118</v>
+      </c>
+      <c r="B96">
+        <v>3</v>
+      </c>
+      <c r="C96" t="s">
+        <v>121</v>
+      </c>
+      <c r="D96" t="s">
+        <v>10</v>
+      </c>
+    </row>
+    <row r="97" spans="1:4">
+      <c r="A97" s="1" t="s">
+        <v>118</v>
+      </c>
+      <c r="B97">
+        <v>4</v>
+      </c>
+      <c r="C97" t="s">
+        <v>122</v>
+      </c>
+      <c r="D97" t="s">
+        <v>10</v>
+      </c>
+    </row>
+    <row r="98" spans="1:4">
+      <c r="A98" s="1" t="s">
+        <v>123</v>
+      </c>
+      <c r="B98">
+        <v>1</v>
+      </c>
+      <c r="C98" t="s">
+        <v>124</v>
+      </c>
+      <c r="D98" t="s">
+        <v>6</v>
+      </c>
+    </row>
+    <row r="99" spans="1:4">
+      <c r="A99" s="1" t="s">
+        <v>123</v>
+      </c>
+      <c r="B99">
+        <v>2</v>
+      </c>
+      <c r="C99" t="s">
+        <v>125</v>
+      </c>
+      <c r="D99" t="s">
+        <v>16</v>
+      </c>
+    </row>
+    <row r="100" spans="1:4">
+      <c r="A100" s="1" t="s">
+        <v>123</v>
+      </c>
+      <c r="B100">
+        <v>3</v>
+      </c>
+      <c r="C100" t="s">
+        <v>126</v>
+      </c>
+      <c r="D100" t="s">
+        <v>10</v>
+      </c>
+    </row>
+    <row r="101" spans="1:4">
+      <c r="A101" s="1" t="s">
+        <v>123</v>
+      </c>
+      <c r="B101">
+        <v>4</v>
+      </c>
+      <c r="C101" t="s">
+        <v>127</v>
+      </c>
+      <c r="D101" t="s">
+        <v>10</v>
+      </c>
+    </row>
+    <row r="102" spans="1:4">
+      <c r="A102" s="1" t="s">
+        <v>128</v>
+      </c>
+      <c r="B102">
+        <v>1</v>
+      </c>
+      <c r="C102" t="s">
+        <v>129</v>
+      </c>
+      <c r="D102" t="s">
+        <v>6</v>
+      </c>
+    </row>
+    <row r="103" spans="1:4">
+      <c r="A103" s="1" t="s">
+        <v>128</v>
+      </c>
+      <c r="B103">
+        <v>2</v>
+      </c>
+      <c r="C103" t="s">
+        <v>130</v>
+      </c>
+      <c r="D103" t="s">
+        <v>16</v>
+      </c>
+    </row>
+    <row r="104" spans="1:4">
+      <c r="A104" s="1" t="s">
+        <v>128</v>
+      </c>
+      <c r="B104">
+        <v>3</v>
+      </c>
+      <c r="C104" t="s">
+        <v>131</v>
+      </c>
+      <c r="D104" t="s">
+        <v>10</v>
+      </c>
+    </row>
+    <row r="105" spans="1:4">
+      <c r="A105" s="1" t="s">
+        <v>128</v>
+      </c>
+      <c r="B105">
+        <v>4</v>
+      </c>
+      <c r="C105" t="s">
+        <v>132</v>
+      </c>
+      <c r="D105" t="s">
+        <v>10</v>
+      </c>
+    </row>
+    <row r="106" spans="1:4">
+      <c r="A106" s="1" t="s">
+        <v>133</v>
+      </c>
+      <c r="B106">
+        <v>1</v>
+      </c>
+      <c r="C106" t="s">
+        <v>134</v>
+      </c>
+      <c r="D106" t="s">
+        <v>6</v>
+      </c>
+    </row>
+    <row r="107" spans="1:4">
+      <c r="A107" s="1" t="s">
+        <v>133</v>
+      </c>
+      <c r="B107">
+        <v>2</v>
+      </c>
+      <c r="C107" t="s">
+        <v>135</v>
+      </c>
+      <c r="D107" t="s">
+        <v>16</v>
+      </c>
+    </row>
+    <row r="108" spans="1:4">
+      <c r="A108" s="1" t="s">
+        <v>133</v>
+      </c>
+      <c r="B108">
+        <v>3</v>
+      </c>
+      <c r="C108" t="s">
+        <v>136</v>
+      </c>
+      <c r="D108" t="s">
+        <v>10</v>
+      </c>
+    </row>
+    <row r="109" spans="1:4">
+      <c r="A109" s="1" t="s">
+        <v>133</v>
+      </c>
+      <c r="B109">
+        <v>4</v>
+      </c>
+      <c r="C109" t="s">
+        <v>137</v>
+      </c>
+      <c r="D109" t="s">
+        <v>10</v>
+      </c>
+    </row>
+    <row r="110" spans="1:4">
+      <c r="A110" s="1" t="s">
+        <v>138</v>
+      </c>
+      <c r="B110">
+        <v>1</v>
+      </c>
+      <c r="C110" t="s">
+        <v>139</v>
+      </c>
+      <c r="D110" t="s">
+        <v>6</v>
+      </c>
+    </row>
+    <row r="111" spans="1:4">
+      <c r="A111" s="1" t="s">
+        <v>138</v>
+      </c>
+      <c r="B111">
+        <v>2</v>
+      </c>
+      <c r="C111" t="s">
+        <v>140</v>
+      </c>
+      <c r="D111" t="s">
+        <v>16</v>
+      </c>
+    </row>
+    <row r="112" spans="1:4">
+      <c r="A112" s="1" t="s">
+        <v>138</v>
+      </c>
+      <c r="B112">
+        <v>3</v>
+      </c>
+      <c r="C112" t="s">
+        <v>141</v>
+      </c>
+      <c r="D112" t="s">
+        <v>10</v>
+      </c>
+    </row>
+    <row r="113" spans="1:4">
+      <c r="A113" s="1" t="s">
+        <v>138</v>
+      </c>
+      <c r="B113">
+        <v>4</v>
+      </c>
+      <c r="C113" t="s">
+        <v>142</v>
+      </c>
+      <c r="D113" t="s">
+        <v>10</v>
+      </c>
+    </row>
+    <row r="114" spans="1:4">
+      <c r="A114" s="1" t="s">
+        <v>143</v>
+      </c>
+      <c r="B114">
+        <v>1</v>
+      </c>
+      <c r="C114" t="s">
+        <v>144</v>
+      </c>
+      <c r="D114" t="s">
+        <v>6</v>
+      </c>
+    </row>
+    <row r="115" spans="1:4">
+      <c r="A115" s="1" t="s">
+        <v>143</v>
+      </c>
+      <c r="B115">
+        <v>2</v>
+      </c>
+      <c r="C115" t="s">
+        <v>145</v>
+      </c>
+      <c r="D115" t="s">
+        <v>16</v>
+      </c>
+    </row>
+    <row r="116" spans="1:4">
+      <c r="A116" s="1" t="s">
+        <v>143</v>
+      </c>
+      <c r="B116">
+        <v>3</v>
+      </c>
+      <c r="C116" t="s">
+        <v>146</v>
+      </c>
+      <c r="D116" t="s">
+        <v>10</v>
+      </c>
+    </row>
+    <row r="117" spans="1:4">
+      <c r="A117" s="1" t="s">
+        <v>143</v>
+      </c>
+      <c r="B117">
+        <v>4</v>
+      </c>
+      <c r="C117" t="s">
+        <v>147</v>
+      </c>
+      <c r="D117" t="s">
+        <v>10</v>
+      </c>
+    </row>
+    <row r="118" spans="1:4">
+      <c r="A118" s="1" t="s">
+        <v>148</v>
+      </c>
+      <c r="B118">
+        <v>1</v>
+      </c>
+      <c r="C118" t="s">
+        <v>149</v>
+      </c>
+      <c r="D118" t="s">
+        <v>6</v>
+      </c>
+    </row>
+    <row r="119" spans="1:4">
+      <c r="A119" s="1" t="s">
+        <v>148</v>
+      </c>
+      <c r="B119">
+        <v>2</v>
+      </c>
+      <c r="C119" t="s">
+        <v>150</v>
+      </c>
+      <c r="D119" t="s">
+        <v>16</v>
+      </c>
+    </row>
+    <row r="120" spans="1:4">
+      <c r="A120" s="1" t="s">
+        <v>148</v>
+      </c>
+      <c r="B120">
+        <v>3</v>
+      </c>
+      <c r="C120" t="s">
+        <v>151</v>
+      </c>
+      <c r="D120" t="s">
+        <v>10</v>
+      </c>
+    </row>
+    <row r="121" spans="1:4">
+      <c r="A121" s="1" t="s">
+        <v>148</v>
+      </c>
+      <c r="B121">
+        <v>4</v>
+      </c>
+      <c r="C121" t="s">
+        <v>152</v>
+      </c>
+      <c r="D121" t="s">
+        <v>10</v>
+      </c>
+    </row>
+    <row r="122" spans="1:4">
+      <c r="A122" s="1" t="s">
+        <v>153</v>
+      </c>
+      <c r="B122">
+        <v>1</v>
+      </c>
+      <c r="C122" t="s">
+        <v>154</v>
+      </c>
+      <c r="D122" t="s">
+        <v>6</v>
+      </c>
+    </row>
+    <row r="123" spans="1:4">
+      <c r="A123" s="1" t="s">
+        <v>153</v>
+      </c>
+      <c r="B123">
+        <v>2</v>
+      </c>
+      <c r="C123" t="s">
+        <v>155</v>
+      </c>
+      <c r="D123" t="s">
+        <v>16</v>
+      </c>
+    </row>
+    <row r="124" spans="1:4">
+      <c r="A124" s="1" t="s">
+        <v>153</v>
+      </c>
+      <c r="B124">
+        <v>3</v>
+      </c>
+      <c r="C124" t="s">
+        <v>156</v>
+      </c>
+      <c r="D124" t="s">
+        <v>10</v>
+      </c>
+    </row>
+    <row r="125" spans="1:4">
+      <c r="A125" s="1" t="s">
+        <v>153</v>
+      </c>
+      <c r="B125">
+        <v>4</v>
+      </c>
+      <c r="C125" t="s">
+        <v>157</v>
+      </c>
+      <c r="D125" t="s">
+        <v>10</v>
+      </c>
+    </row>
+    <row r="126" spans="1:4">
+      <c r="A126" s="1" t="s">
+        <v>158</v>
+      </c>
+      <c r="B126">
+        <v>1</v>
+      </c>
+      <c r="C126" t="s">
+        <v>47</v>
+      </c>
+      <c r="D126" t="s">
+        <v>6</v>
+      </c>
+    </row>
+    <row r="127" spans="1:4">
+      <c r="A127" s="1" t="s">
+        <v>158</v>
+      </c>
+      <c r="B127">
+        <v>2</v>
+      </c>
+      <c r="C127" t="s">
+        <v>159</v>
+      </c>
+      <c r="D127" t="s">
+        <v>16</v>
+      </c>
+    </row>
+    <row r="128" spans="1:4">
+      <c r="A128" s="1" t="s">
+        <v>158</v>
+      </c>
+      <c r="B128">
+        <v>3</v>
+      </c>
+      <c r="C128" t="s">
+        <v>160</v>
+      </c>
+      <c r="D128" t="s">
+        <v>10</v>
+      </c>
+    </row>
+    <row r="129" spans="1:4">
+      <c r="A129" s="1" t="s">
+        <v>158</v>
+      </c>
+      <c r="B129">
+        <v>4</v>
+      </c>
+      <c r="C129" t="s">
+        <v>161</v>
+      </c>
+      <c r="D129" t="s">
+        <v>10</v>
+      </c>
+    </row>
+    <row r="130" spans="1:4">
+      <c r="A130" s="1" t="s">
+        <v>162</v>
+      </c>
+      <c r="B130">
+        <v>1</v>
+      </c>
+      <c r="C130" t="s">
+        <v>154</v>
+      </c>
+      <c r="D130" t="s">
+        <v>6</v>
+      </c>
+    </row>
+    <row r="131" spans="1:4">
+      <c r="A131" s="1" t="s">
+        <v>162</v>
+      </c>
+      <c r="B131">
+        <v>2</v>
+      </c>
+      <c r="C131" t="s">
+        <v>163</v>
+      </c>
+      <c r="D131" t="s">
+        <v>16</v>
+      </c>
+    </row>
+    <row r="132" spans="1:4">
+      <c r="A132" s="1" t="s">
+        <v>162</v>
+      </c>
+      <c r="B132">
+        <v>3</v>
+      </c>
+      <c r="C132" t="s">
+        <v>164</v>
+      </c>
+      <c r="D132" t="s">
+        <v>10</v>
+      </c>
+    </row>
+    <row r="133" spans="1:4">
+      <c r="A133" s="1" t="s">
+        <v>162</v>
+      </c>
+      <c r="B133">
+        <v>4</v>
+      </c>
+      <c r="C133" t="s">
+        <v>165</v>
+      </c>
+      <c r="D133" t="s">
+        <v>10</v>
+      </c>
+    </row>
+    <row r="134" spans="1:4">
+      <c r="A134" s="1" t="s">
+        <v>166</v>
+      </c>
+      <c r="B134">
+        <v>1</v>
+      </c>
+      <c r="C134" t="s">
+        <v>154</v>
+      </c>
+      <c r="D134" t="s">
+        <v>6</v>
+      </c>
+    </row>
+    <row r="135" spans="1:4">
+      <c r="A135" s="1" t="s">
+        <v>166</v>
+      </c>
+      <c r="B135">
+        <v>2</v>
+      </c>
+      <c r="C135" t="s">
+        <v>167</v>
+      </c>
+      <c r="D135" t="s">
+        <v>16</v>
+      </c>
+    </row>
+    <row r="136" spans="1:4">
+      <c r="A136" s="1" t="s">
+        <v>166</v>
+      </c>
+      <c r="B136">
+        <v>3</v>
+      </c>
+      <c r="C136" t="s">
+        <v>168</v>
+      </c>
+      <c r="D136" t="s">
+        <v>10</v>
+      </c>
+    </row>
+    <row r="137" spans="1:4">
+      <c r="A137" s="1" t="s">
+        <v>166</v>
+      </c>
+      <c r="B137">
+        <v>4</v>
+      </c>
+      <c r="C137" t="s">
+        <v>169</v>
+      </c>
+      <c r="D137" t="s">
+        <v>10</v>
+      </c>
+    </row>
+    <row r="138" spans="1:4">
+      <c r="A138" s="1" t="s">
+        <v>170</v>
+      </c>
+      <c r="B138">
+        <v>1</v>
+      </c>
+      <c r="C138" t="s">
+        <v>154</v>
+      </c>
+      <c r="D138" t="s">
+        <v>6</v>
+      </c>
+    </row>
+    <row r="139" spans="1:4">
+      <c r="A139" s="1" t="s">
+        <v>170</v>
+      </c>
+      <c r="B139">
+        <v>2</v>
+      </c>
+      <c r="C139" t="s">
+        <v>171</v>
+      </c>
+      <c r="D139" t="s">
+        <v>16</v>
+      </c>
+    </row>
+    <row r="140" spans="1:4">
+      <c r="A140" s="1" t="s">
+        <v>170</v>
+      </c>
+      <c r="B140">
+        <v>3</v>
+      </c>
+      <c r="C140" t="s">
+        <v>172</v>
+      </c>
+      <c r="D140" t="s">
+        <v>10</v>
+      </c>
+    </row>
+    <row r="141" spans="1:4">
+      <c r="A141" s="1" t="s">
+        <v>170</v>
+      </c>
+      <c r="B141">
+        <v>4</v>
+      </c>
+      <c r="C141" t="s">
+        <v>173</v>
+      </c>
+      <c r="D141" t="s">
+        <v>10</v>
+      </c>
+    </row>
+    <row r="142" spans="1:4">
+      <c r="A142" s="1" t="s">
+        <v>174</v>
+      </c>
+      <c r="B142">
+        <v>1</v>
+      </c>
+      <c r="C142" t="s">
+        <v>154</v>
+      </c>
+      <c r="D142" t="s">
+        <v>6</v>
+      </c>
+    </row>
+    <row r="143" spans="1:4">
+      <c r="A143" s="1" t="s">
+        <v>174</v>
+      </c>
+      <c r="B143">
+        <v>2</v>
+      </c>
+      <c r="C143" t="s">
+        <v>175</v>
+      </c>
+      <c r="D143" t="s">
+        <v>16</v>
+      </c>
+    </row>
+    <row r="144" spans="1:4">
+      <c r="A144" s="1" t="s">
+        <v>174</v>
+      </c>
+      <c r="B144">
+        <v>3</v>
+      </c>
+      <c r="C144" t="s">
+        <v>176</v>
+      </c>
+      <c r="D144" t="s">
+        <v>10</v>
+      </c>
+    </row>
+    <row r="145" spans="1:4">
+      <c r="A145" s="1" t="s">
+        <v>174</v>
+      </c>
+      <c r="B145">
+        <v>4</v>
+      </c>
+      <c r="C145" t="s">
+        <v>177</v>
+      </c>
+      <c r="D145" t="s">
+        <v>10</v>
+      </c>
+    </row>
+    <row r="146" spans="1:4">
+      <c r="A146" s="1" t="s">
+        <v>178</v>
+      </c>
+      <c r="B146">
+        <v>1</v>
+      </c>
+      <c r="C146" t="s">
+        <v>179</v>
+      </c>
+      <c r="D146" t="s">
+        <v>6</v>
+      </c>
+    </row>
+    <row r="147" spans="1:4">
+      <c r="A147" s="1" t="s">
+        <v>178</v>
+      </c>
+      <c r="B147">
+        <v>2</v>
+      </c>
+      <c r="C147" t="s">
+        <v>180</v>
+      </c>
+      <c r="D147" t="s">
+        <v>16</v>
+      </c>
+    </row>
+    <row r="148" spans="1:4">
+      <c r="A148" s="1" t="s">
+        <v>178</v>
+      </c>
+      <c r="B148">
+        <v>3</v>
+      </c>
+      <c r="C148" t="s">
+        <v>181</v>
+      </c>
+      <c r="D148" t="s">
+        <v>10</v>
+      </c>
+    </row>
+    <row r="149" spans="1:4">
+      <c r="A149" s="1" t="s">
+        <v>178</v>
+      </c>
+      <c r="B149">
+        <v>4</v>
+      </c>
+      <c r="C149" t="s">
+        <v>182</v>
+      </c>
+      <c r="D149" t="s">
+        <v>10</v>
+      </c>
+    </row>
+    <row r="150" spans="1:4">
+      <c r="A150" s="1" t="s">
+        <v>183</v>
+      </c>
+      <c r="B150">
+        <v>1</v>
+      </c>
+      <c r="C150" t="s">
+        <v>154</v>
+      </c>
+      <c r="D150" t="s">
+        <v>6</v>
+      </c>
+    </row>
+    <row r="151" spans="1:4">
+      <c r="A151" s="1" t="s">
+        <v>183</v>
+      </c>
+      <c r="B151">
+        <v>2</v>
+      </c>
+      <c r="C151" t="s">
+        <v>184</v>
+      </c>
+      <c r="D151" t="s">
+        <v>16</v>
+      </c>
+    </row>
+    <row r="152" spans="1:4">
+      <c r="A152" s="1" t="s">
+        <v>183</v>
+      </c>
+      <c r="B152">
+        <v>3</v>
+      </c>
+      <c r="C152" t="s">
+        <v>185</v>
+      </c>
+      <c r="D152" t="s">
+        <v>10</v>
+      </c>
+    </row>
+    <row r="153" spans="1:4">
+      <c r="A153" s="1" t="s">
+        <v>183</v>
+      </c>
+      <c r="B153">
+        <v>4</v>
+      </c>
+      <c r="C153" t="s">
+        <v>186</v>
+      </c>
+      <c r="D153" t="s">
+        <v>10</v>
+      </c>
+    </row>
+    <row r="154" spans="1:4">
+      <c r="A154" s="1" t="s">
+        <v>187</v>
+      </c>
+      <c r="B154">
+        <v>1</v>
+      </c>
+      <c r="C154" t="s">
+        <v>154</v>
+      </c>
+      <c r="D154" t="s">
+        <v>6</v>
+      </c>
+    </row>
+    <row r="155" spans="1:4">
+      <c r="A155" s="1" t="s">
+        <v>187</v>
+      </c>
+      <c r="B155">
+        <v>2</v>
+      </c>
+      <c r="C155" t="s">
+        <v>188</v>
+      </c>
+      <c r="D155" t="s">
+        <v>16</v>
+      </c>
+    </row>
+    <row r="156" spans="1:4">
+      <c r="A156" s="1" t="s">
+        <v>187</v>
+      </c>
+      <c r="B156">
+        <v>3</v>
+      </c>
+      <c r="C156" t="s">
+        <v>189</v>
+      </c>
+      <c r="D156" t="s">
+        <v>10</v>
+      </c>
+    </row>
+    <row r="157" spans="1:4">
+      <c r="A157" s="1" t="s">
+        <v>187</v>
+      </c>
+      <c r="B157">
+        <v>4</v>
+      </c>
+      <c r="C157" t="s">
+        <v>190</v>
+      </c>
+      <c r="D157" t="s">
+        <v>10</v>
+      </c>
+    </row>
+    <row r="158" spans="1:4">
+      <c r="A158" s="1" t="s">
+        <v>191</v>
+      </c>
+      <c r="B158">
+        <v>1</v>
+      </c>
+      <c r="C158" t="s">
+        <v>154</v>
+      </c>
+      <c r="D158" t="s">
+        <v>6</v>
+      </c>
+    </row>
+    <row r="159" spans="1:4">
+      <c r="A159" s="1" t="s">
+        <v>191</v>
+      </c>
+      <c r="B159">
+        <v>2</v>
+      </c>
+      <c r="C159" t="s">
+        <v>192</v>
+      </c>
+      <c r="D159" t="s">
+        <v>16</v>
+      </c>
+    </row>
+    <row r="160" spans="1:4">
+      <c r="A160" s="1" t="s">
+        <v>191</v>
+      </c>
+      <c r="B160">
+        <v>3</v>
+      </c>
+      <c r="C160" t="s">
+        <v>193</v>
+      </c>
+      <c r="D160" t="s">
+        <v>10</v>
+      </c>
+    </row>
+    <row r="161" spans="1:4">
+      <c r="A161" s="1" t="s">
+        <v>191</v>
+      </c>
+      <c r="B161">
+        <v>4</v>
+      </c>
+      <c r="C161" t="s">
+        <v>194</v>
+      </c>
+      <c r="D161" t="s">
+        <v>10</v>
+      </c>
+    </row>
+    <row r="162" spans="1:4">
+      <c r="A162" s="1" t="s">
+        <v>195</v>
+      </c>
+      <c r="B162">
+        <v>1</v>
+      </c>
+      <c r="C162" t="s">
+        <v>154</v>
+      </c>
+      <c r="D162" t="s">
+        <v>6</v>
+      </c>
+    </row>
+    <row r="163" spans="1:4">
+      <c r="A163" s="1" t="s">
+        <v>195</v>
+      </c>
+      <c r="B163">
+        <v>2</v>
+      </c>
+      <c r="C163" t="s">
+        <v>196</v>
+      </c>
+      <c r="D163" t="s">
+        <v>16</v>
+      </c>
+    </row>
+    <row r="164" spans="1:4">
+      <c r="A164" s="1" t="s">
+        <v>195</v>
+      </c>
+      <c r="B164">
+        <v>3</v>
+      </c>
+      <c r="C164" t="s">
+        <v>197</v>
+      </c>
+      <c r="D164" t="s">
+        <v>10</v>
+      </c>
+    </row>
+    <row r="165" spans="1:4">
+      <c r="A165" s="1" t="s">
+        <v>195</v>
+      </c>
+      <c r="B165">
+        <v>4</v>
+      </c>
+      <c r="C165" t="s">
+        <v>198</v>
+      </c>
+      <c r="D165" t="s">
+        <v>10</v>
+      </c>
+    </row>
+    <row r="166" spans="1:4">
+      <c r="A166" s="1" t="s">
+        <v>199</v>
+      </c>
+      <c r="B166">
+        <v>1</v>
+      </c>
+      <c r="C166" t="s">
+        <v>154</v>
+      </c>
+      <c r="D166" t="s">
+        <v>6</v>
+      </c>
+    </row>
+    <row r="167" spans="1:4">
+      <c r="A167" s="1" t="s">
+        <v>199</v>
+      </c>
+      <c r="B167">
+        <v>2</v>
+      </c>
+      <c r="C167" t="s">
+        <v>200</v>
+      </c>
+      <c r="D167" t="s">
+        <v>16</v>
+      </c>
+    </row>
+    <row r="168" spans="1:4">
+      <c r="A168" s="1" t="s">
+        <v>199</v>
+      </c>
+      <c r="B168">
+        <v>3</v>
+      </c>
+      <c r="C168" t="s">
+        <v>201</v>
+      </c>
+      <c r="D168" t="s">
+        <v>10</v>
+      </c>
+    </row>
+    <row r="169" spans="1:4">
+      <c r="A169" s="1" t="s">
+        <v>199</v>
+      </c>
+      <c r="B169">
+        <v>4</v>
+      </c>
+      <c r="C169" t="s">
+        <v>202</v>
+      </c>
+      <c r="D169" t="s">
+        <v>10</v>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
   <headerFooter/>

--- a/data/简答题题库.xlsx
+++ b/data/简答题题库.xlsx
@@ -27,7 +27,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="512" uniqueCount="203">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="500" uniqueCount="202">
   <si>
     <t>疾病</t>
   </si>
@@ -353,7 +353,7 @@
     <t>结合全部情境，讨论肺癌骨转移的综合治疗策略及预后管理。</t>
   </si>
   <si>
-    <t>“脑中风的警报”</t>
+    <t>“半身风云”</t>
   </si>
   <si>
     <t>根据情境2，解释缺血性脑卒中的治疗原则及溶栓治疗的适应证。</t>
@@ -363,9 +363,6 @@
   </si>
   <si>
     <t>结合全部情境，列出脑梗死患者的出院指导及长期管理要点。</t>
-  </si>
-  <si>
-    <t>“半身风云”</t>
   </si>
   <si>
     <t>“惊厥之舞”</t>
@@ -1600,7 +1597,7 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:etc="http://www.wps.cn/officeDocument/2017/etCustomData">
   <sheetPr/>
-  <dimension ref="A1:D169"/>
+  <dimension ref="A1:D165"/>
   <sheetFormatPr defaultColWidth="9" defaultRowHeight="13.5" outlineLevelCol="3"/>
   <cols>
     <col min="1" max="1" width="9.02654867256637" style="1"/>
@@ -2804,7 +2801,7 @@
         <v>1</v>
       </c>
       <c r="C86" t="s">
-        <v>47</v>
+        <v>113</v>
       </c>
       <c r="D86" t="s">
         <v>6</v>
@@ -2818,7 +2815,7 @@
         <v>2</v>
       </c>
       <c r="C87" t="s">
-        <v>109</v>
+        <v>114</v>
       </c>
       <c r="D87" t="s">
         <v>16</v>
@@ -2832,7 +2829,7 @@
         <v>3</v>
       </c>
       <c r="C88" t="s">
-        <v>110</v>
+        <v>115</v>
       </c>
       <c r="D88" t="s">
         <v>10</v>
@@ -2846,7 +2843,7 @@
         <v>4</v>
       </c>
       <c r="C89" t="s">
-        <v>111</v>
+        <v>116</v>
       </c>
       <c r="D89" t="s">
         <v>10</v>
@@ -2854,13 +2851,13 @@
     </row>
     <row r="90" spans="1:4">
       <c r="A90" s="1" t="s">
-        <v>113</v>
+        <v>117</v>
       </c>
       <c r="B90">
         <v>1</v>
       </c>
       <c r="C90" t="s">
-        <v>114</v>
+        <v>118</v>
       </c>
       <c r="D90" t="s">
         <v>6</v>
@@ -2868,13 +2865,13 @@
     </row>
     <row r="91" spans="1:4">
       <c r="A91" s="1" t="s">
-        <v>113</v>
+        <v>117</v>
       </c>
       <c r="B91">
         <v>2</v>
       </c>
       <c r="C91" t="s">
-        <v>115</v>
+        <v>119</v>
       </c>
       <c r="D91" t="s">
         <v>16</v>
@@ -2882,13 +2879,13 @@
     </row>
     <row r="92" spans="1:4">
       <c r="A92" s="1" t="s">
-        <v>113</v>
+        <v>117</v>
       </c>
       <c r="B92">
         <v>3</v>
       </c>
       <c r="C92" t="s">
-        <v>116</v>
+        <v>120</v>
       </c>
       <c r="D92" t="s">
         <v>10</v>
@@ -2896,13 +2893,13 @@
     </row>
     <row r="93" spans="1:4">
       <c r="A93" s="1" t="s">
-        <v>113</v>
+        <v>117</v>
       </c>
       <c r="B93">
         <v>4</v>
       </c>
       <c r="C93" t="s">
-        <v>117</v>
+        <v>121</v>
       </c>
       <c r="D93" t="s">
         <v>10</v>
@@ -2910,13 +2907,13 @@
     </row>
     <row r="94" spans="1:4">
       <c r="A94" s="1" t="s">
-        <v>118</v>
+        <v>122</v>
       </c>
       <c r="B94">
         <v>1</v>
       </c>
       <c r="C94" t="s">
-        <v>119</v>
+        <v>123</v>
       </c>
       <c r="D94" t="s">
         <v>6</v>
@@ -2924,13 +2921,13 @@
     </row>
     <row r="95" spans="1:4">
       <c r="A95" s="1" t="s">
-        <v>118</v>
+        <v>122</v>
       </c>
       <c r="B95">
         <v>2</v>
       </c>
       <c r="C95" t="s">
-        <v>120</v>
+        <v>124</v>
       </c>
       <c r="D95" t="s">
         <v>16</v>
@@ -2938,13 +2935,13 @@
     </row>
     <row r="96" spans="1:4">
       <c r="A96" s="1" t="s">
-        <v>118</v>
+        <v>122</v>
       </c>
       <c r="B96">
         <v>3</v>
       </c>
       <c r="C96" t="s">
-        <v>121</v>
+        <v>125</v>
       </c>
       <c r="D96" t="s">
         <v>10</v>
@@ -2952,13 +2949,13 @@
     </row>
     <row r="97" spans="1:4">
       <c r="A97" s="1" t="s">
-        <v>118</v>
+        <v>122</v>
       </c>
       <c r="B97">
         <v>4</v>
       </c>
       <c r="C97" t="s">
-        <v>122</v>
+        <v>126</v>
       </c>
       <c r="D97" t="s">
         <v>10</v>
@@ -2966,13 +2963,13 @@
     </row>
     <row r="98" spans="1:4">
       <c r="A98" s="1" t="s">
-        <v>123</v>
+        <v>127</v>
       </c>
       <c r="B98">
         <v>1</v>
       </c>
       <c r="C98" t="s">
-        <v>124</v>
+        <v>128</v>
       </c>
       <c r="D98" t="s">
         <v>6</v>
@@ -2980,13 +2977,13 @@
     </row>
     <row r="99" spans="1:4">
       <c r="A99" s="1" t="s">
-        <v>123</v>
+        <v>127</v>
       </c>
       <c r="B99">
         <v>2</v>
       </c>
       <c r="C99" t="s">
-        <v>125</v>
+        <v>129</v>
       </c>
       <c r="D99" t="s">
         <v>16</v>
@@ -2994,13 +2991,13 @@
     </row>
     <row r="100" spans="1:4">
       <c r="A100" s="1" t="s">
-        <v>123</v>
+        <v>127</v>
       </c>
       <c r="B100">
         <v>3</v>
       </c>
       <c r="C100" t="s">
-        <v>126</v>
+        <v>130</v>
       </c>
       <c r="D100" t="s">
         <v>10</v>
@@ -3008,13 +3005,13 @@
     </row>
     <row r="101" spans="1:4">
       <c r="A101" s="1" t="s">
-        <v>123</v>
+        <v>127</v>
       </c>
       <c r="B101">
         <v>4</v>
       </c>
       <c r="C101" t="s">
-        <v>127</v>
+        <v>131</v>
       </c>
       <c r="D101" t="s">
         <v>10</v>
@@ -3022,13 +3019,13 @@
     </row>
     <row r="102" spans="1:4">
       <c r="A102" s="1" t="s">
-        <v>128</v>
+        <v>132</v>
       </c>
       <c r="B102">
         <v>1</v>
       </c>
       <c r="C102" t="s">
-        <v>129</v>
+        <v>133</v>
       </c>
       <c r="D102" t="s">
         <v>6</v>
@@ -3036,13 +3033,13 @@
     </row>
     <row r="103" spans="1:4">
       <c r="A103" s="1" t="s">
-        <v>128</v>
+        <v>132</v>
       </c>
       <c r="B103">
         <v>2</v>
       </c>
       <c r="C103" t="s">
-        <v>130</v>
+        <v>134</v>
       </c>
       <c r="D103" t="s">
         <v>16</v>
@@ -3050,13 +3047,13 @@
     </row>
     <row r="104" spans="1:4">
       <c r="A104" s="1" t="s">
-        <v>128</v>
+        <v>132</v>
       </c>
       <c r="B104">
         <v>3</v>
       </c>
       <c r="C104" t="s">
-        <v>131</v>
+        <v>135</v>
       </c>
       <c r="D104" t="s">
         <v>10</v>
@@ -3064,13 +3061,13 @@
     </row>
     <row r="105" spans="1:4">
       <c r="A105" s="1" t="s">
-        <v>128</v>
+        <v>132</v>
       </c>
       <c r="B105">
         <v>4</v>
       </c>
       <c r="C105" t="s">
-        <v>132</v>
+        <v>136</v>
       </c>
       <c r="D105" t="s">
         <v>10</v>
@@ -3078,13 +3075,13 @@
     </row>
     <row r="106" spans="1:4">
       <c r="A106" s="1" t="s">
-        <v>133</v>
+        <v>137</v>
       </c>
       <c r="B106">
         <v>1</v>
       </c>
       <c r="C106" t="s">
-        <v>134</v>
+        <v>138</v>
       </c>
       <c r="D106" t="s">
         <v>6</v>
@@ -3092,13 +3089,13 @@
     </row>
     <row r="107" spans="1:4">
       <c r="A107" s="1" t="s">
-        <v>133</v>
+        <v>137</v>
       </c>
       <c r="B107">
         <v>2</v>
       </c>
       <c r="C107" t="s">
-        <v>135</v>
+        <v>139</v>
       </c>
       <c r="D107" t="s">
         <v>16</v>
@@ -3106,13 +3103,13 @@
     </row>
     <row r="108" spans="1:4">
       <c r="A108" s="1" t="s">
-        <v>133</v>
+        <v>137</v>
       </c>
       <c r="B108">
         <v>3</v>
       </c>
       <c r="C108" t="s">
-        <v>136</v>
+        <v>140</v>
       </c>
       <c r="D108" t="s">
         <v>10</v>
@@ -3120,13 +3117,13 @@
     </row>
     <row r="109" spans="1:4">
       <c r="A109" s="1" t="s">
-        <v>133</v>
+        <v>137</v>
       </c>
       <c r="B109">
         <v>4</v>
       </c>
       <c r="C109" t="s">
-        <v>137</v>
+        <v>141</v>
       </c>
       <c r="D109" t="s">
         <v>10</v>
@@ -3134,13 +3131,13 @@
     </row>
     <row r="110" spans="1:4">
       <c r="A110" s="1" t="s">
-        <v>138</v>
+        <v>142</v>
       </c>
       <c r="B110">
         <v>1</v>
       </c>
       <c r="C110" t="s">
-        <v>139</v>
+        <v>143</v>
       </c>
       <c r="D110" t="s">
         <v>6</v>
@@ -3148,13 +3145,13 @@
     </row>
     <row r="111" spans="1:4">
       <c r="A111" s="1" t="s">
-        <v>138</v>
+        <v>142</v>
       </c>
       <c r="B111">
         <v>2</v>
       </c>
       <c r="C111" t="s">
-        <v>140</v>
+        <v>144</v>
       </c>
       <c r="D111" t="s">
         <v>16</v>
@@ -3162,13 +3159,13 @@
     </row>
     <row r="112" spans="1:4">
       <c r="A112" s="1" t="s">
-        <v>138</v>
+        <v>142</v>
       </c>
       <c r="B112">
         <v>3</v>
       </c>
       <c r="C112" t="s">
-        <v>141</v>
+        <v>145</v>
       </c>
       <c r="D112" t="s">
         <v>10</v>
@@ -3176,13 +3173,13 @@
     </row>
     <row r="113" spans="1:4">
       <c r="A113" s="1" t="s">
-        <v>138</v>
+        <v>142</v>
       </c>
       <c r="B113">
         <v>4</v>
       </c>
       <c r="C113" t="s">
-        <v>142</v>
+        <v>146</v>
       </c>
       <c r="D113" t="s">
         <v>10</v>
@@ -3190,13 +3187,13 @@
     </row>
     <row r="114" spans="1:4">
       <c r="A114" s="1" t="s">
-        <v>143</v>
+        <v>147</v>
       </c>
       <c r="B114">
         <v>1</v>
       </c>
       <c r="C114" t="s">
-        <v>144</v>
+        <v>148</v>
       </c>
       <c r="D114" t="s">
         <v>6</v>
@@ -3204,13 +3201,13 @@
     </row>
     <row r="115" spans="1:4">
       <c r="A115" s="1" t="s">
-        <v>143</v>
+        <v>147</v>
       </c>
       <c r="B115">
         <v>2</v>
       </c>
       <c r="C115" t="s">
-        <v>145</v>
+        <v>149</v>
       </c>
       <c r="D115" t="s">
         <v>16</v>
@@ -3218,13 +3215,13 @@
     </row>
     <row r="116" spans="1:4">
       <c r="A116" s="1" t="s">
-        <v>143</v>
+        <v>147</v>
       </c>
       <c r="B116">
         <v>3</v>
       </c>
       <c r="C116" t="s">
-        <v>146</v>
+        <v>150</v>
       </c>
       <c r="D116" t="s">
         <v>10</v>
@@ -3232,13 +3229,13 @@
     </row>
     <row r="117" spans="1:4">
       <c r="A117" s="1" t="s">
-        <v>143</v>
+        <v>147</v>
       </c>
       <c r="B117">
         <v>4</v>
       </c>
       <c r="C117" t="s">
-        <v>147</v>
+        <v>151</v>
       </c>
       <c r="D117" t="s">
         <v>10</v>
@@ -3246,13 +3243,13 @@
     </row>
     <row r="118" spans="1:4">
       <c r="A118" s="1" t="s">
-        <v>148</v>
+        <v>152</v>
       </c>
       <c r="B118">
         <v>1</v>
       </c>
       <c r="C118" t="s">
-        <v>149</v>
+        <v>153</v>
       </c>
       <c r="D118" t="s">
         <v>6</v>
@@ -3260,13 +3257,13 @@
     </row>
     <row r="119" spans="1:4">
       <c r="A119" s="1" t="s">
-        <v>148</v>
+        <v>152</v>
       </c>
       <c r="B119">
         <v>2</v>
       </c>
       <c r="C119" t="s">
-        <v>150</v>
+        <v>154</v>
       </c>
       <c r="D119" t="s">
         <v>16</v>
@@ -3274,13 +3271,13 @@
     </row>
     <row r="120" spans="1:4">
       <c r="A120" s="1" t="s">
-        <v>148</v>
+        <v>152</v>
       </c>
       <c r="B120">
         <v>3</v>
       </c>
       <c r="C120" t="s">
-        <v>151</v>
+        <v>155</v>
       </c>
       <c r="D120" t="s">
         <v>10</v>
@@ -3288,13 +3285,13 @@
     </row>
     <row r="121" spans="1:4">
       <c r="A121" s="1" t="s">
-        <v>148</v>
+        <v>152</v>
       </c>
       <c r="B121">
         <v>4</v>
       </c>
       <c r="C121" t="s">
-        <v>152</v>
+        <v>156</v>
       </c>
       <c r="D121" t="s">
         <v>10</v>
@@ -3302,13 +3299,13 @@
     </row>
     <row r="122" spans="1:4">
       <c r="A122" s="1" t="s">
-        <v>153</v>
+        <v>157</v>
       </c>
       <c r="B122">
         <v>1</v>
       </c>
       <c r="C122" t="s">
-        <v>154</v>
+        <v>47</v>
       </c>
       <c r="D122" t="s">
         <v>6</v>
@@ -3316,13 +3313,13 @@
     </row>
     <row r="123" spans="1:4">
       <c r="A123" s="1" t="s">
-        <v>153</v>
+        <v>157</v>
       </c>
       <c r="B123">
         <v>2</v>
       </c>
       <c r="C123" t="s">
-        <v>155</v>
+        <v>158</v>
       </c>
       <c r="D123" t="s">
         <v>16</v>
@@ -3330,13 +3327,13 @@
     </row>
     <row r="124" spans="1:4">
       <c r="A124" s="1" t="s">
-        <v>153</v>
+        <v>157</v>
       </c>
       <c r="B124">
         <v>3</v>
       </c>
       <c r="C124" t="s">
-        <v>156</v>
+        <v>159</v>
       </c>
       <c r="D124" t="s">
         <v>10</v>
@@ -3344,13 +3341,13 @@
     </row>
     <row r="125" spans="1:4">
       <c r="A125" s="1" t="s">
-        <v>153</v>
+        <v>157</v>
       </c>
       <c r="B125">
         <v>4</v>
       </c>
       <c r="C125" t="s">
-        <v>157</v>
+        <v>160</v>
       </c>
       <c r="D125" t="s">
         <v>10</v>
@@ -3358,13 +3355,13 @@
     </row>
     <row r="126" spans="1:4">
       <c r="A126" s="1" t="s">
-        <v>158</v>
+        <v>161</v>
       </c>
       <c r="B126">
         <v>1</v>
       </c>
       <c r="C126" t="s">
-        <v>47</v>
+        <v>153</v>
       </c>
       <c r="D126" t="s">
         <v>6</v>
@@ -3372,13 +3369,13 @@
     </row>
     <row r="127" spans="1:4">
       <c r="A127" s="1" t="s">
-        <v>158</v>
+        <v>161</v>
       </c>
       <c r="B127">
         <v>2</v>
       </c>
       <c r="C127" t="s">
-        <v>159</v>
+        <v>162</v>
       </c>
       <c r="D127" t="s">
         <v>16</v>
@@ -3386,13 +3383,13 @@
     </row>
     <row r="128" spans="1:4">
       <c r="A128" s="1" t="s">
-        <v>158</v>
+        <v>161</v>
       </c>
       <c r="B128">
         <v>3</v>
       </c>
       <c r="C128" t="s">
-        <v>160</v>
+        <v>163</v>
       </c>
       <c r="D128" t="s">
         <v>10</v>
@@ -3400,13 +3397,13 @@
     </row>
     <row r="129" spans="1:4">
       <c r="A129" s="1" t="s">
-        <v>158</v>
+        <v>161</v>
       </c>
       <c r="B129">
         <v>4</v>
       </c>
       <c r="C129" t="s">
-        <v>161</v>
+        <v>164</v>
       </c>
       <c r="D129" t="s">
         <v>10</v>
@@ -3414,13 +3411,13 @@
     </row>
     <row r="130" spans="1:4">
       <c r="A130" s="1" t="s">
-        <v>162</v>
+        <v>165</v>
       </c>
       <c r="B130">
         <v>1</v>
       </c>
       <c r="C130" t="s">
-        <v>154</v>
+        <v>153</v>
       </c>
       <c r="D130" t="s">
         <v>6</v>
@@ -3428,13 +3425,13 @@
     </row>
     <row r="131" spans="1:4">
       <c r="A131" s="1" t="s">
-        <v>162</v>
+        <v>165</v>
       </c>
       <c r="B131">
         <v>2</v>
       </c>
       <c r="C131" t="s">
-        <v>163</v>
+        <v>166</v>
       </c>
       <c r="D131" t="s">
         <v>16</v>
@@ -3442,13 +3439,13 @@
     </row>
     <row r="132" spans="1:4">
       <c r="A132" s="1" t="s">
-        <v>162</v>
+        <v>165</v>
       </c>
       <c r="B132">
         <v>3</v>
       </c>
       <c r="C132" t="s">
-        <v>164</v>
+        <v>167</v>
       </c>
       <c r="D132" t="s">
         <v>10</v>
@@ -3456,13 +3453,13 @@
     </row>
     <row r="133" spans="1:4">
       <c r="A133" s="1" t="s">
-        <v>162</v>
+        <v>165</v>
       </c>
       <c r="B133">
         <v>4</v>
       </c>
       <c r="C133" t="s">
-        <v>165</v>
+        <v>168</v>
       </c>
       <c r="D133" t="s">
         <v>10</v>
@@ -3470,13 +3467,13 @@
     </row>
     <row r="134" spans="1:4">
       <c r="A134" s="1" t="s">
-        <v>166</v>
+        <v>169</v>
       </c>
       <c r="B134">
         <v>1</v>
       </c>
       <c r="C134" t="s">
-        <v>154</v>
+        <v>153</v>
       </c>
       <c r="D134" t="s">
         <v>6</v>
@@ -3484,13 +3481,13 @@
     </row>
     <row r="135" spans="1:4">
       <c r="A135" s="1" t="s">
-        <v>166</v>
+        <v>169</v>
       </c>
       <c r="B135">
         <v>2</v>
       </c>
       <c r="C135" t="s">
-        <v>167</v>
+        <v>170</v>
       </c>
       <c r="D135" t="s">
         <v>16</v>
@@ -3498,13 +3495,13 @@
     </row>
     <row r="136" spans="1:4">
       <c r="A136" s="1" t="s">
-        <v>166</v>
+        <v>169</v>
       </c>
       <c r="B136">
         <v>3</v>
       </c>
       <c r="C136" t="s">
-        <v>168</v>
+        <v>171</v>
       </c>
       <c r="D136" t="s">
         <v>10</v>
@@ -3512,13 +3509,13 @@
     </row>
     <row r="137" spans="1:4">
       <c r="A137" s="1" t="s">
-        <v>166</v>
+        <v>169</v>
       </c>
       <c r="B137">
         <v>4</v>
       </c>
       <c r="C137" t="s">
-        <v>169</v>
+        <v>172</v>
       </c>
       <c r="D137" t="s">
         <v>10</v>
@@ -3526,13 +3523,13 @@
     </row>
     <row r="138" spans="1:4">
       <c r="A138" s="1" t="s">
-        <v>170</v>
+        <v>173</v>
       </c>
       <c r="B138">
         <v>1</v>
       </c>
       <c r="C138" t="s">
-        <v>154</v>
+        <v>153</v>
       </c>
       <c r="D138" t="s">
         <v>6</v>
@@ -3540,13 +3537,13 @@
     </row>
     <row r="139" spans="1:4">
       <c r="A139" s="1" t="s">
-        <v>170</v>
+        <v>173</v>
       </c>
       <c r="B139">
         <v>2</v>
       </c>
       <c r="C139" t="s">
-        <v>171</v>
+        <v>174</v>
       </c>
       <c r="D139" t="s">
         <v>16</v>
@@ -3554,13 +3551,13 @@
     </row>
     <row r="140" spans="1:4">
       <c r="A140" s="1" t="s">
-        <v>170</v>
+        <v>173</v>
       </c>
       <c r="B140">
         <v>3</v>
       </c>
       <c r="C140" t="s">
-        <v>172</v>
+        <v>175</v>
       </c>
       <c r="D140" t="s">
         <v>10</v>
@@ -3568,13 +3565,13 @@
     </row>
     <row r="141" spans="1:4">
       <c r="A141" s="1" t="s">
-        <v>170</v>
+        <v>173</v>
       </c>
       <c r="B141">
         <v>4</v>
       </c>
       <c r="C141" t="s">
-        <v>173</v>
+        <v>176</v>
       </c>
       <c r="D141" t="s">
         <v>10</v>
@@ -3582,13 +3579,13 @@
     </row>
     <row r="142" spans="1:4">
       <c r="A142" s="1" t="s">
-        <v>174</v>
+        <v>177</v>
       </c>
       <c r="B142">
         <v>1</v>
       </c>
       <c r="C142" t="s">
-        <v>154</v>
+        <v>178</v>
       </c>
       <c r="D142" t="s">
         <v>6</v>
@@ -3596,13 +3593,13 @@
     </row>
     <row r="143" spans="1:4">
       <c r="A143" s="1" t="s">
-        <v>174</v>
+        <v>177</v>
       </c>
       <c r="B143">
         <v>2</v>
       </c>
       <c r="C143" t="s">
-        <v>175</v>
+        <v>179</v>
       </c>
       <c r="D143" t="s">
         <v>16</v>
@@ -3610,13 +3607,13 @@
     </row>
     <row r="144" spans="1:4">
       <c r="A144" s="1" t="s">
-        <v>174</v>
+        <v>177</v>
       </c>
       <c r="B144">
         <v>3</v>
       </c>
       <c r="C144" t="s">
-        <v>176</v>
+        <v>180</v>
       </c>
       <c r="D144" t="s">
         <v>10</v>
@@ -3624,13 +3621,13 @@
     </row>
     <row r="145" spans="1:4">
       <c r="A145" s="1" t="s">
-        <v>174</v>
+        <v>177</v>
       </c>
       <c r="B145">
         <v>4</v>
       </c>
       <c r="C145" t="s">
-        <v>177</v>
+        <v>181</v>
       </c>
       <c r="D145" t="s">
         <v>10</v>
@@ -3638,13 +3635,13 @@
     </row>
     <row r="146" spans="1:4">
       <c r="A146" s="1" t="s">
-        <v>178</v>
+        <v>182</v>
       </c>
       <c r="B146">
         <v>1</v>
       </c>
       <c r="C146" t="s">
-        <v>179</v>
+        <v>153</v>
       </c>
       <c r="D146" t="s">
         <v>6</v>
@@ -3652,13 +3649,13 @@
     </row>
     <row r="147" spans="1:4">
       <c r="A147" s="1" t="s">
-        <v>178</v>
+        <v>182</v>
       </c>
       <c r="B147">
         <v>2</v>
       </c>
       <c r="C147" t="s">
-        <v>180</v>
+        <v>183</v>
       </c>
       <c r="D147" t="s">
         <v>16</v>
@@ -3666,13 +3663,13 @@
     </row>
     <row r="148" spans="1:4">
       <c r="A148" s="1" t="s">
-        <v>178</v>
+        <v>182</v>
       </c>
       <c r="B148">
         <v>3</v>
       </c>
       <c r="C148" t="s">
-        <v>181</v>
+        <v>184</v>
       </c>
       <c r="D148" t="s">
         <v>10</v>
@@ -3680,13 +3677,13 @@
     </row>
     <row r="149" spans="1:4">
       <c r="A149" s="1" t="s">
-        <v>178</v>
+        <v>182</v>
       </c>
       <c r="B149">
         <v>4</v>
       </c>
       <c r="C149" t="s">
-        <v>182</v>
+        <v>185</v>
       </c>
       <c r="D149" t="s">
         <v>10</v>
@@ -3694,13 +3691,13 @@
     </row>
     <row r="150" spans="1:4">
       <c r="A150" s="1" t="s">
-        <v>183</v>
+        <v>186</v>
       </c>
       <c r="B150">
         <v>1</v>
       </c>
       <c r="C150" t="s">
-        <v>154</v>
+        <v>153</v>
       </c>
       <c r="D150" t="s">
         <v>6</v>
@@ -3708,13 +3705,13 @@
     </row>
     <row r="151" spans="1:4">
       <c r="A151" s="1" t="s">
-        <v>183</v>
+        <v>186</v>
       </c>
       <c r="B151">
         <v>2</v>
       </c>
       <c r="C151" t="s">
-        <v>184</v>
+        <v>187</v>
       </c>
       <c r="D151" t="s">
         <v>16</v>
@@ -3722,13 +3719,13 @@
     </row>
     <row r="152" spans="1:4">
       <c r="A152" s="1" t="s">
-        <v>183</v>
+        <v>186</v>
       </c>
       <c r="B152">
         <v>3</v>
       </c>
       <c r="C152" t="s">
-        <v>185</v>
+        <v>188</v>
       </c>
       <c r="D152" t="s">
         <v>10</v>
@@ -3736,13 +3733,13 @@
     </row>
     <row r="153" spans="1:4">
       <c r="A153" s="1" t="s">
-        <v>183</v>
+        <v>186</v>
       </c>
       <c r="B153">
         <v>4</v>
       </c>
       <c r="C153" t="s">
-        <v>186</v>
+        <v>189</v>
       </c>
       <c r="D153" t="s">
         <v>10</v>
@@ -3750,13 +3747,13 @@
     </row>
     <row r="154" spans="1:4">
       <c r="A154" s="1" t="s">
-        <v>187</v>
+        <v>190</v>
       </c>
       <c r="B154">
         <v>1</v>
       </c>
       <c r="C154" t="s">
-        <v>154</v>
+        <v>153</v>
       </c>
       <c r="D154" t="s">
         <v>6</v>
@@ -3764,13 +3761,13 @@
     </row>
     <row r="155" spans="1:4">
       <c r="A155" s="1" t="s">
-        <v>187</v>
+        <v>190</v>
       </c>
       <c r="B155">
         <v>2</v>
       </c>
       <c r="C155" t="s">
-        <v>188</v>
+        <v>191</v>
       </c>
       <c r="D155" t="s">
         <v>16</v>
@@ -3778,13 +3775,13 @@
     </row>
     <row r="156" spans="1:4">
       <c r="A156" s="1" t="s">
-        <v>187</v>
+        <v>190</v>
       </c>
       <c r="B156">
         <v>3</v>
       </c>
       <c r="C156" t="s">
-        <v>189</v>
+        <v>192</v>
       </c>
       <c r="D156" t="s">
         <v>10</v>
@@ -3792,13 +3789,13 @@
     </row>
     <row r="157" spans="1:4">
       <c r="A157" s="1" t="s">
-        <v>187</v>
+        <v>190</v>
       </c>
       <c r="B157">
         <v>4</v>
       </c>
       <c r="C157" t="s">
-        <v>190</v>
+        <v>193</v>
       </c>
       <c r="D157" t="s">
         <v>10</v>
@@ -3806,13 +3803,13 @@
     </row>
     <row r="158" spans="1:4">
       <c r="A158" s="1" t="s">
-        <v>191</v>
+        <v>194</v>
       </c>
       <c r="B158">
         <v>1</v>
       </c>
       <c r="C158" t="s">
-        <v>154</v>
+        <v>153</v>
       </c>
       <c r="D158" t="s">
         <v>6</v>
@@ -3820,13 +3817,13 @@
     </row>
     <row r="159" spans="1:4">
       <c r="A159" s="1" t="s">
-        <v>191</v>
+        <v>194</v>
       </c>
       <c r="B159">
         <v>2</v>
       </c>
       <c r="C159" t="s">
-        <v>192</v>
+        <v>195</v>
       </c>
       <c r="D159" t="s">
         <v>16</v>
@@ -3834,13 +3831,13 @@
     </row>
     <row r="160" spans="1:4">
       <c r="A160" s="1" t="s">
-        <v>191</v>
+        <v>194</v>
       </c>
       <c r="B160">
         <v>3</v>
       </c>
       <c r="C160" t="s">
-        <v>193</v>
+        <v>196</v>
       </c>
       <c r="D160" t="s">
         <v>10</v>
@@ -3848,13 +3845,13 @@
     </row>
     <row r="161" spans="1:4">
       <c r="A161" s="1" t="s">
-        <v>191</v>
+        <v>194</v>
       </c>
       <c r="B161">
         <v>4</v>
       </c>
       <c r="C161" t="s">
-        <v>194</v>
+        <v>197</v>
       </c>
       <c r="D161" t="s">
         <v>10</v>
@@ -3862,13 +3859,13 @@
     </row>
     <row r="162" spans="1:4">
       <c r="A162" s="1" t="s">
-        <v>195</v>
+        <v>198</v>
       </c>
       <c r="B162">
         <v>1</v>
       </c>
       <c r="C162" t="s">
-        <v>154</v>
+        <v>153</v>
       </c>
       <c r="D162" t="s">
         <v>6</v>
@@ -3876,13 +3873,13 @@
     </row>
     <row r="163" spans="1:4">
       <c r="A163" s="1" t="s">
-        <v>195</v>
+        <v>198</v>
       </c>
       <c r="B163">
         <v>2</v>
       </c>
       <c r="C163" t="s">
-        <v>196</v>
+        <v>199</v>
       </c>
       <c r="D163" t="s">
         <v>16</v>
@@ -3890,13 +3887,13 @@
     </row>
     <row r="164" spans="1:4">
       <c r="A164" s="1" t="s">
-        <v>195</v>
+        <v>198</v>
       </c>
       <c r="B164">
         <v>3</v>
       </c>
       <c r="C164" t="s">
-        <v>197</v>
+        <v>200</v>
       </c>
       <c r="D164" t="s">
         <v>10</v>
@@ -3904,71 +3901,15 @@
     </row>
     <row r="165" spans="1:4">
       <c r="A165" s="1" t="s">
-        <v>195</v>
+        <v>198</v>
       </c>
       <c r="B165">
         <v>4</v>
       </c>
       <c r="C165" t="s">
-        <v>198</v>
+        <v>201</v>
       </c>
       <c r="D165" t="s">
-        <v>10</v>
-      </c>
-    </row>
-    <row r="166" spans="1:4">
-      <c r="A166" s="1" t="s">
-        <v>199</v>
-      </c>
-      <c r="B166">
-        <v>1</v>
-      </c>
-      <c r="C166" t="s">
-        <v>154</v>
-      </c>
-      <c r="D166" t="s">
-        <v>6</v>
-      </c>
-    </row>
-    <row r="167" spans="1:4">
-      <c r="A167" s="1" t="s">
-        <v>199</v>
-      </c>
-      <c r="B167">
-        <v>2</v>
-      </c>
-      <c r="C167" t="s">
-        <v>200</v>
-      </c>
-      <c r="D167" t="s">
-        <v>16</v>
-      </c>
-    </row>
-    <row r="168" spans="1:4">
-      <c r="A168" s="1" t="s">
-        <v>199</v>
-      </c>
-      <c r="B168">
-        <v>3</v>
-      </c>
-      <c r="C168" t="s">
-        <v>201</v>
-      </c>
-      <c r="D168" t="s">
-        <v>10</v>
-      </c>
-    </row>
-    <row r="169" spans="1:4">
-      <c r="A169" s="1" t="s">
-        <v>199</v>
-      </c>
-      <c r="B169">
-        <v>4</v>
-      </c>
-      <c r="C169" t="s">
-        <v>202</v>
-      </c>
-      <c r="D169" t="s">
         <v>10</v>
       </c>
     </row>
